--- a/data/batches/B15_TrialSummary_TS_part3/Test_Validation_Report/Test_Validation_Report_B15.xlsx
+++ b/data/batches/B15_TrialSummary_TS_part3/Test_Validation_Report/Test_Validation_Report_B15.xlsx
@@ -1933,11 +1933,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2012,11 +2008,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2091,11 +2083,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2170,11 +2158,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2249,11 +2233,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2328,11 +2308,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2407,11 +2383,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2486,11 +2458,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2565,11 +2533,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2644,11 +2608,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2723,11 +2683,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2802,11 +2758,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2881,11 +2833,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -2956,11 +2904,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3031,11 +2975,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3106,11 +3046,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3181,11 +3117,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3256,11 +3188,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3331,11 +3259,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3406,11 +3330,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3481,11 +3401,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3556,11 +3472,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3631,11 +3543,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3706,11 +3614,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3781,11 +3685,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3856,11 +3756,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -3931,11 +3827,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4006,11 +3898,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4081,11 +3969,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4156,11 +4040,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4231,11 +4111,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4306,11 +4182,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4381,11 +4253,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4456,11 +4324,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4531,11 +4395,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4606,11 +4466,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4681,11 +4537,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4756,11 +4608,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4831,11 +4679,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4906,11 +4750,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -4981,11 +4821,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -5056,11 +4892,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -5131,11 +4963,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -5206,11 +5034,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -5281,11 +5105,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>TSVALNF</t>
